--- a/business_surveys/022_corporate_ethics_perception_survey--business_surveys.xlsx
+++ b/business_surveys/022_corporate_ethics_perception_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>general_concept</t>
+          <t>overall_ethics_concept</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>General Concept</t>
+          <t>Overall ethics concept</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>reporting_incidents</t>
+          <t>reporting_channel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>reporting incidents</t>
+          <t>Reporting channel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ethics_training</t>
+          <t>reporting_frequency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ethics training</t>
+          <t>Reporting frequency</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>reporting_channels</t>
+          <t>behavior_when_faced_with_incident</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>reporting channels</t>
+          <t>Reporting behavior when faced with an incident</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>reporting_frequency</t>
+          <t>reporting_via_email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>reporting frequency</t>
+          <t>Reporting via email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>behavior_reporting</t>
+          <t>reporting_via_phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>reporting behavior</t>
+          <t>Reporting via phone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>reporting_reporting</t>
+          <t>reporting_frequency_via_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>reporting reporting</t>
+          <t>Reporting frequency via email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>reporting_reporting_channels_1</t>
+          <t>reporting_frequency_via_phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>reporting channels</t>
+          <t>Reporting frequency via phone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>reporting_frequency_1</t>
+          <t>reporting_behavior</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>reporting frequency</t>
+          <t>Overall reporting behavior</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>reporting_behavior_reporting_1</t>
+          <t>behavior_faced_with_incident</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>reporting behavior</t>
+          <t>Behavior Faced With Incident</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>reporting_reporting_1</t>
+          <t>overall_reporting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>reporting reporting</t>
+          <t>Overall reporting</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,44 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>reporting_channels_1</t>
+          <t>reporting_frequency_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>reporting channels</t>
+          <t>Reporting Frequency 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>reporting_frequency_1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>reporting frequency</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,357 +827,255 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ethics_training_choices</t>
+          <t>reporting_channel_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ethics_training_choices</t>
+          <t>reporting_channel_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ethics_training_choices</t>
+          <t>reporting_channel_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'unsure'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Unsure'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>reporting_channels_choices</t>
+          <t>reporting_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>reporting_channels_choices</t>
+          <t>reporting_frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reporting_channels_choices</t>
+          <t>reporting_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'in-person'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'In-person'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>reporting_frequency_choices</t>
+          <t>reporting_frequency_via_email_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>reporting_frequency_choices</t>
+          <t>reporting_frequency_via_email_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>reporting_frequency_choices</t>
+          <t>reporting_frequency_via_email_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>reporting_reporting_channels_1_choices</t>
+          <t>reporting_frequency_via_phone_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reporting_reporting_channels_1_choices</t>
+          <t>reporting_frequency_via_phone_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>reporting_reporting_channels_1_choices</t>
+          <t>reporting_frequency_via_phone_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'in-person'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'In-person'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>reporting_frequency_1_choices</t>
+          <t>reporting_frequency_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>reporting_frequency_1_choices</t>
+          <t>reporting_frequency_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>reporting_frequency_1_choices</t>
+          <t>reporting_frequency_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>reporting_channels_1_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'value':_'email'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'value': 'Email'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>reporting_channels_1_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'value':_'phone'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'value': 'Phone'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>reporting_channels_1_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'value':_'in-person'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'value': 'In-person'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>reporting_frequency_1_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'value':_'daily'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'value': 'Daily'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>reporting_frequency_1_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'value':_'weekly'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'value': 'Weekly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>reporting_frequency_1_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'value':_'monthly'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
